--- a/artfynd/A 1164-2026 artfynd.xlsx
+++ b/artfynd/A 1164-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1406,6 +1406,357 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130852736</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Igeltjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>527676</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6722286</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rätt färska.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130852452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527685</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6722094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130852869</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Igeltjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527645</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6722289</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lite färskare.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1164-2026 artfynd.xlsx
+++ b/artfynd/A 1164-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>46455912</v>
+        <v>61455549</v>
       </c>
       <c r="B2" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102995</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +705,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527651.2617949685</v>
+        <v>527651</v>
       </c>
       <c r="R2" t="n">
-        <v>6722168.676196555</v>
+        <v>6722169</v>
       </c>
       <c r="S2" t="n">
         <v>108</v>
@@ -754,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-28</t>
+          <t>2016-09-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-28</t>
+          <t>2016-09-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,49 +781,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Wallström</t>
+          <t>Anders Westman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Wallström</t>
+          <t>Anders Westman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47892008</v>
+        <v>38200070</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,9 +826,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527651.2617949685</v>
+        <v>527651</v>
       </c>
       <c r="R3" t="n">
-        <v>6722168.676196555</v>
+        <v>6722169</v>
       </c>
       <c r="S3" t="n">
         <v>108</v>
@@ -875,27 +867,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-12-31</t>
+          <t>1977-06-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-12-31</t>
+          <t>1977-06-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kråkmyran</t>
+          <t>Ingvar Bonde (Angivet i DOF arkiv: 1 outfärgad hane 1977). Meddelanden nr 1 1978 sid. 17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,27 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Wallström</t>
+          <t>Lars Hansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Wallström</t>
+          <t>Via Lars Hansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61455549</v>
+        <v>130852452</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,16 +942,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527651.2617949685</v>
+        <v>527685</v>
       </c>
       <c r="R4" t="n">
-        <v>6722168.676196555</v>
+        <v>6722094</v>
       </c>
       <c r="S4" t="n">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,22 +984,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-17</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,61 +1019,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Westman</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Westman</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61455547</v>
+        <v>22132149</v>
       </c>
       <c r="B5" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1096,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527651.2617949685</v>
+        <v>527651</v>
       </c>
       <c r="R5" t="n">
-        <v>6722168.676196555</v>
+        <v>6722169</v>
       </c>
       <c r="S5" t="n">
         <v>108</v>
@@ -1126,22 +1105,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-17</t>
+          <t>2005-11-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-17</t>
+          <t>2005-11-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,68 +1135,71 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Westman</t>
+          <t>Lotta Bonde</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Westman</t>
+          <t>Lotta Bonde</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66814472</v>
+        <v>61455547</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkmyran, Dlr</t>
+          <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527455.4944287499</v>
+        <v>527651</v>
       </c>
       <c r="R6" t="n">
-        <v>6722190.727957613</v>
+        <v>6722169</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1223,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-07-21</t>
+          <t>2016-09-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-07-21</t>
+          <t>2016-09-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,27 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Anders Westman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Anders Westman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121561918</v>
+        <v>22130843</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,32 +1276,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
@@ -1361,27 +1344,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2005-11-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2005-11-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På skidspåret nära Tunnan där den spelgalna tjädern höll till i våras. Spår och spillning nytillkomna sedan igår.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,65 +1374,71 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Nihlberg</t>
+          <t>Lotta Bonde</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Nihlberg</t>
+          <t>Lotta Bonde</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130852736</v>
+        <v>61305327</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>57785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>102622</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Igeltjärnsberget, Igeltjärnsberget, Dlr</t>
+          <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527676</v>
+        <v>527651</v>
       </c>
       <c r="R8" t="n">
-        <v>6722286</v>
+        <v>6722169</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,27 +1462,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2016-09-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2016-09-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rätt färska.</t>
+          <t>Satt i en liten tall när jag kom gående på berget mellan Igeltjärn och L. Åltjärn. Stångtjärnsområdet. Lyfte sedan och flög in i granskogen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,50 +1497,59 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars Wallström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars Wallström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130852452</v>
+        <v>46464615</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>58039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102626</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1565,13 +1558,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527685</v>
+        <v>527651</v>
       </c>
       <c r="R9" t="n">
-        <v>6722094</v>
+        <v>6722169</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1595,27 +1588,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2013-06-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2013-06-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,65 +1618,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars Wallström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars Wallström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130852869</v>
+        <v>100149129</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>58497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Igeltjärnsberget, Igeltjärnsberget, Dlr</t>
+          <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527645</v>
+        <v>527651</v>
       </c>
       <c r="R10" t="n">
-        <v>6722289</v>
+        <v>6722169</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1712,27 +1704,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lite färskare.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,15 +1734,586 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Lars Wallström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Wallström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>46455912</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527651</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6722169</v>
+      </c>
+      <c r="S11" t="n">
+        <v>108</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-06-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-06-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Wallström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Wallström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>47892008</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Stångtjärn, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>527651</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6722169</v>
+      </c>
+      <c r="S12" t="n">
+        <v>108</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kråkmyran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Wallström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Wallström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130852736</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Igeltjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>527676</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6722286</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rätt färska.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130852869</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Igeltjärnsberget, Igeltjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>527645</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6722289</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lite färskare.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>66814472</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kråkmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>527455</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6722191</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-07-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-07-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1164-2026 artfynd.xlsx
+++ b/artfynd/A 1164-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61455549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/38200070</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130852452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22132149</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61455547</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22130843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61305327</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1627,6 +1667,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/46464615</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1743,6 +1788,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100149129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1859,6 +1909,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/46455912</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1980,6 +2035,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47892008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2097,6 +2157,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130852736</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2214,6 +2279,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130852869</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2314,8 +2384,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66814472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>